--- a/docs/downloads/05/tbl_house_status_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_house_status_alaotra_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Prêtée</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -746,12 +740,6 @@
         <is>
           <t>En location</t>
         </is>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1.4</v>
       </c>
     </row>
     <row r="23">

--- a/docs/downloads/05/tbl_house_status_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_house_status_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
